--- a/Result/profitability/4116.xlsx
+++ b/Result/profitability/4116.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM62"/>
+  <dimension ref="A1:AM63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.32</v>
       </c>
       <c r="M2" t="n">
-        <v>0.44375</v>
+        <v>0.5337500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>31.67625</v>
+        <v>31.89875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.9</v>
       </c>
       <c r="M3" t="n">
-        <v>0.48125</v>
+        <v>0.5725</v>
       </c>
       <c r="N3" t="n">
-        <v>32.1525</v>
+        <v>32.335</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -801,7 +801,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.21</v>
       </c>
       <c r="M4" t="n">
-        <v>0.43375</v>
+        <v>0.53625</v>
       </c>
       <c r="N4" t="n">
-        <v>32.3125</v>
+        <v>32.31625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4575</v>
+        <v>0.595</v>
       </c>
       <c r="N5" t="n">
-        <v>33.19</v>
+        <v>33.35</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.15</v>
       </c>
       <c r="M6" t="n">
-        <v>0.57375</v>
+        <v>0.66125</v>
       </c>
       <c r="N6" t="n">
-        <v>35.17</v>
+        <v>35.14624999999999</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1149,7 +1149,7 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -1158,7 +1158,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.89</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6074999999999999</v>
+        <v>0.7200000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>36.18875</v>
+        <v>36.1175</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -8302,6 +8302,133 @@
       </c>
       <c r="AM62" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>4116</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1429</v>
+      </c>
+      <c r="D63" t="n">
+        <v>968</v>
+      </c>
+      <c r="E63" t="n">
+        <v>461</v>
+      </c>
+      <c r="F63" t="n">
+        <v>32.29</v>
+      </c>
+      <c r="G63" t="n">
+        <v>90</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>6.28%</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>50</v>
+      </c>
+      <c r="J63" t="n">
+        <v>140</v>
+      </c>
+      <c r="K63" t="n">
+        <v>59</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.56875</v>
+      </c>
+      <c r="N63" t="n">
+        <v>31.81125</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1</v>
+      </c>
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
+      </c>
+      <c r="V63" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X63" t="n">
+        <v>3.714285714285714</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0.03999999999999915</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0.001240310077519347</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1.279999999999998</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0.04127700741696216</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK63" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
